--- a/output/graficos_dimensiones/comunal_d_depmay_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:41</t>
+    <t xml:space="preserve">2026-08-17 21:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:37</t>
+    <t xml:space="preserve">2026-09-01 17:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmay_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmay_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:41</t>
+    <t xml:space="preserve">2026-09-06 22:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
